--- a/ig/DM-AVRIL-2026/ValueSet-jdv-trod-examen-cisis.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-jdv-trod-examen-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Cannabinoïdes [Présence/Seuil] Urine ; Qualitatif ; Dépistage</t>
   </si>
   <si>
-    <t>18725-2</t>
+    <t>72885-7</t>
   </si>
   <si>
     <t>Virus respiratoire syncytial Ag [Présence/Seuil] Nasopharynx ; Qualitatif ; Immunoanalyse rapide</t>
@@ -276,7 +276,7 @@
     <t>5803-2</t>
   </si>
   <si>
-    <t>pH [Log de concentration] Urine ; Numérique ; Bandelette réactive</t>
+    <t>pH [Log de concentration] Urine ; Semi-Quantitatif ; Bandelette réactive</t>
   </si>
   <si>
     <t>5804-0</t>
@@ -288,7 +288,7 @@
     <t>5811-5</t>
   </si>
   <si>
-    <t>Densité [Densité relative] Urine ; Semi-Quantitatif ; Bandelette réactive</t>
+    <t>Observation [Densité] Urine ; Semi-Quantitatif ; Bandelette réactive</t>
   </si>
   <si>
     <t>58941-6</t>
@@ -354,13 +354,13 @@
     <t>80382-5</t>
   </si>
   <si>
-    <t>Influenza virus A Ag [Présence/Seuil] Voies respiratoires supérieures ; Qualitatif ; Immunoanalyse rapide</t>
+    <t>Influenza virus A Ag [Présence/Seuil] Échantillon du système respiratoire supérieur ; Qualitatif ; Immunoanalyse rapide</t>
   </si>
   <si>
     <t>80383-3</t>
   </si>
   <si>
-    <t>Influenza virus B Ag [Présence/Seuil] Voies respiratoires supérieures ; Qualitatif ; Immunoanalyse rapide</t>
+    <t>Influenza virus B Ag [Présence/Seuil] Échantillon du système respiratoire supérieur ; Qualitatif ; Immunoanalyse rapide</t>
   </si>
   <si>
     <t>80387-4</t>
@@ -372,7 +372,7 @@
     <t>94558-4</t>
   </si>
   <si>
-    <t>Coronavirus SARS-CoV-2 Ag [Présence/Seuil] Respiratoire ; Qualitatif ; Immunoanalyse rapide</t>
+    <t>Coronavirus SARS-CoV-2 Ag [Présence/Seuil] Échantillon du système respiratoire ; Qualitatif ; Immunoanalyse rapide</t>
   </si>
   <si>
     <t/>
